--- a/Deterministic/Model Files/Segment Test/data/production_capacity_scenarios_NEW_11SEP.xlsx
+++ b/Deterministic/Model Files/Segment Test/data/production_capacity_scenarios_NEW_11SEP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/Model Files/L-Shaped/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/Deterministic/Model Files/Segment Test/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{15A1990F-446C-4531-B793-C24CD42A570E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C273C5F3-914D-42FF-86D6-7E7B28401061}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{15A1990F-446C-4531-B793-C24CD42A570E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{879BADB5-DFF7-4D8B-8A39-CA32313BA1E1}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_capacity" sheetId="1" r:id="rId1"/>
@@ -167,10 +167,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -505,34 +501,34 @@
         <v>15</v>
       </c>
       <c r="B2" s="2">
-        <v>876700000.00000012</v>
+        <v>5201000</v>
       </c>
       <c r="C2" s="2">
-        <v>899800000.00000012</v>
+        <v>7140000</v>
       </c>
       <c r="D2" s="2">
-        <v>939400000.00000012</v>
+        <v>8329999.9999999991</v>
       </c>
       <c r="E2" s="2">
-        <v>870100000.00000012</v>
+        <v>8329999.9999999991</v>
       </c>
       <c r="F2" s="2">
-        <v>898700000.00000012</v>
+        <v>8259999.9999999991</v>
       </c>
       <c r="G2" s="2">
-        <v>899800000.00000012</v>
+        <v>8189999.9999999991</v>
       </c>
       <c r="H2" s="2">
-        <v>592900000</v>
+        <v>8329999.9999999991</v>
       </c>
       <c r="I2" s="2">
-        <v>682000000</v>
+        <v>8189999.9999999991</v>
       </c>
       <c r="J2" s="2">
-        <v>606100000</v>
+        <v>8329999.9999999991</v>
       </c>
       <c r="K2" s="2">
-        <v>639100000</v>
+        <v>8470000</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -540,34 +536,34 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>353100000</v>
+        <v>36400000</v>
       </c>
       <c r="C3" s="2">
-        <v>370700000.00000006</v>
+        <v>40460000</v>
       </c>
       <c r="D3" s="2">
-        <v>405900000.00000006</v>
+        <v>40740000</v>
       </c>
       <c r="E3" s="2">
-        <v>411400000.00000006</v>
+        <v>38500000</v>
       </c>
       <c r="F3" s="2">
-        <v>436700000.00000006</v>
+        <v>38360000</v>
       </c>
       <c r="G3" s="2">
-        <v>470800000.00000006</v>
+        <v>38150000</v>
       </c>
       <c r="H3" s="2">
-        <v>394900000.00000006</v>
+        <v>38430000</v>
       </c>
       <c r="I3" s="2">
-        <v>432300000.00000006</v>
+        <v>38150000</v>
       </c>
       <c r="J3" s="2">
-        <v>404800000.00000006</v>
+        <v>38640000</v>
       </c>
       <c r="K3" s="2">
-        <v>418000000.00000006</v>
+        <v>39060000</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -575,34 +571,34 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>183700000</v>
+        <v>53270000</v>
       </c>
       <c r="C4" s="2">
-        <v>204600000.00000003</v>
+        <v>58939999.999999993</v>
       </c>
       <c r="D4" s="2">
-        <v>206800000.00000003</v>
+        <v>59989999.999999993</v>
       </c>
       <c r="E4" s="2">
-        <v>196900000.00000003</v>
+        <v>58100000</v>
       </c>
       <c r="F4" s="2">
-        <v>194700000.00000003</v>
+        <v>58450000</v>
       </c>
       <c r="G4" s="2">
-        <v>190300000.00000003</v>
+        <v>56490000</v>
       </c>
       <c r="H4" s="2">
-        <v>742500000.00000012</v>
+        <v>3779999.9999999995</v>
       </c>
       <c r="I4" s="2">
-        <v>739200000.00000012</v>
+        <v>3737999.9999999995</v>
       </c>
       <c r="J4" s="2">
-        <v>742500000.00000012</v>
+        <v>3779999.9999999995</v>
       </c>
       <c r="K4" s="2">
-        <v>744700000.00000012</v>
+        <v>3821999.9999999995</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -610,34 +606,34 @@
         <v>8</v>
       </c>
       <c r="B5" s="2">
-        <v>112200000.00000001</v>
+        <v>8119999.9999999991</v>
       </c>
       <c r="C5" s="2">
-        <v>123200000.00000001</v>
+        <v>11130000</v>
       </c>
       <c r="D5" s="2">
-        <v>125400000.00000001</v>
+        <v>13020000</v>
       </c>
       <c r="E5" s="2">
-        <v>121000000.00000001</v>
+        <v>12950000</v>
       </c>
       <c r="F5" s="2">
-        <v>121000000.00000001</v>
+        <v>12950000</v>
       </c>
       <c r="G5" s="2">
-        <v>116600000.00000001</v>
+        <v>12740000</v>
       </c>
       <c r="H5" s="2">
-        <v>0</v>
+        <v>13020000</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>12810000</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>13020000</v>
       </c>
       <c r="K5" s="2">
-        <v>0</v>
+        <v>13230000</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -645,34 +641,34 @@
         <v>12</v>
       </c>
       <c r="B6" s="2">
-        <v>99660000.000000015</v>
+        <v>116900000</v>
       </c>
       <c r="C6" s="2">
-        <v>118800000.00000001</v>
+        <v>130199999.99999999</v>
       </c>
       <c r="D6" s="2">
-        <v>133100000.00000001</v>
+        <v>131599999.99999999</v>
       </c>
       <c r="E6" s="2">
-        <v>130900000.00000001</v>
+        <v>125299999.99999999</v>
       </c>
       <c r="F6" s="2">
-        <v>140800000</v>
+        <v>123899999.99999999</v>
       </c>
       <c r="G6" s="2">
-        <v>139700000</v>
+        <v>121099999.99999999</v>
       </c>
       <c r="H6" s="2">
-        <v>141900000</v>
+        <v>472499999.99999994</v>
       </c>
       <c r="I6" s="2">
-        <v>138600000</v>
+        <v>470399999.99999994</v>
       </c>
       <c r="J6" s="2">
-        <v>139700000</v>
+        <v>472499999.99999994</v>
       </c>
       <c r="K6" s="2">
-        <v>139700000</v>
+        <v>473899999.99999994</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -680,34 +676,34 @@
         <v>14</v>
       </c>
       <c r="B7" s="2">
-        <v>99550000.000000015</v>
+        <v>9730000</v>
       </c>
       <c r="C7" s="2">
-        <v>128700000.00000001</v>
+        <v>10640000</v>
       </c>
       <c r="D7" s="2">
-        <v>144100000</v>
+        <v>11060000</v>
       </c>
       <c r="E7" s="2">
-        <v>143000000</v>
+        <v>11900000</v>
       </c>
       <c r="F7" s="2">
-        <v>143000000</v>
+        <v>12390000</v>
       </c>
       <c r="G7" s="2">
-        <v>140800000</v>
+        <v>11270000</v>
       </c>
       <c r="H7" s="2">
-        <v>109890000.00000001</v>
+        <v>1113000</v>
       </c>
       <c r="I7" s="2">
-        <v>108130000.00000001</v>
+        <v>1113000</v>
       </c>
       <c r="J7" s="2">
-        <v>110000000.00000001</v>
+        <v>889000</v>
       </c>
       <c r="K7" s="2">
-        <v>112200000.00000001</v>
+        <v>923999.99999999988</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -715,34 +711,34 @@
         <v>9</v>
       </c>
       <c r="B8" s="2">
-        <v>87230000</v>
+        <v>224700000</v>
       </c>
       <c r="C8" s="2">
-        <v>99550000.000000015</v>
+        <v>235899999.99999997</v>
       </c>
       <c r="D8" s="2">
-        <v>103400000.00000001</v>
+        <v>258299999.99999997</v>
       </c>
       <c r="E8" s="2">
-        <v>98450000.000000015</v>
+        <v>261799999.99999997</v>
       </c>
       <c r="F8" s="2">
-        <v>98010000.000000015</v>
+        <v>277900000</v>
       </c>
       <c r="G8" s="2">
-        <v>96140000.000000015</v>
+        <v>299600000</v>
       </c>
       <c r="H8" s="2">
-        <v>97350000.000000015</v>
+        <v>251299999.99999997</v>
       </c>
       <c r="I8" s="2">
-        <v>95920000.000000015</v>
+        <v>275100000</v>
       </c>
       <c r="J8" s="2">
-        <v>97130000.000000015</v>
+        <v>257599999.99999997</v>
       </c>
       <c r="K8" s="2">
-        <v>98120000.000000015</v>
+        <v>265999999.99999997</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -750,34 +746,34 @@
         <v>3</v>
       </c>
       <c r="B9" s="2">
-        <v>75339000</v>
+        <v>71400000</v>
       </c>
       <c r="C9" s="2">
-        <v>83358000</v>
+        <v>78400000</v>
       </c>
       <c r="D9" s="2">
-        <v>84843000</v>
+        <v>79800000</v>
       </c>
       <c r="E9" s="2">
-        <v>82170000</v>
+        <v>77000000</v>
       </c>
       <c r="F9" s="2">
-        <v>82665000</v>
+        <v>77000000</v>
       </c>
       <c r="G9" s="2">
-        <v>79893000</v>
+        <v>74200000</v>
       </c>
       <c r="H9" s="2">
-        <v>5346000</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>5286600</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>5346000</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2">
-        <v>5405400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -785,34 +781,34 @@
         <v>13</v>
       </c>
       <c r="B10" s="2">
-        <v>68420000</v>
+        <v>55510000</v>
       </c>
       <c r="C10" s="2">
-        <v>82280000</v>
+        <v>63349999.999999993</v>
       </c>
       <c r="D10" s="2">
-        <v>80410000</v>
+        <v>65799999.999999993</v>
       </c>
       <c r="E10" s="2">
-        <v>73590000</v>
+        <v>62649999.999999993</v>
       </c>
       <c r="F10" s="2">
-        <v>76780000</v>
+        <v>62369999.999999993</v>
       </c>
       <c r="G10" s="2">
-        <v>64570000.000000007</v>
+        <v>61179999.999999993</v>
       </c>
       <c r="H10" s="2">
-        <v>48400000.000000007</v>
+        <v>61949999.999999993</v>
       </c>
       <c r="I10" s="2">
-        <v>45980000</v>
+        <v>61039999.999999993</v>
       </c>
       <c r="J10" s="2">
-        <v>46640000.000000007</v>
+        <v>61809999.999999993</v>
       </c>
       <c r="K10" s="2">
-        <v>47080000.000000007</v>
+        <v>62439999.999999993</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -820,34 +816,34 @@
         <v>2</v>
       </c>
       <c r="B11" s="2">
-        <v>57200000.000000007</v>
+        <v>11830000</v>
       </c>
       <c r="C11" s="2">
-        <v>63580000.000000007</v>
+        <v>11970000</v>
       </c>
       <c r="D11" s="2">
-        <v>64020000.000000007</v>
+        <v>17500000</v>
       </c>
       <c r="E11" s="2">
-        <v>60500000.000000007</v>
+        <v>46480000</v>
       </c>
       <c r="F11" s="2">
-        <v>60280000.000000007</v>
+        <v>59149999.999999993</v>
       </c>
       <c r="G11" s="2">
-        <v>59950000.000000007</v>
+        <v>41300000</v>
       </c>
       <c r="H11" s="2">
-        <v>60390000.000000007</v>
+        <v>26950000</v>
       </c>
       <c r="I11" s="2">
-        <v>59950000.000000007</v>
+        <v>27020000</v>
       </c>
       <c r="J11" s="2">
-        <v>60720000.000000007</v>
+        <v>21490000</v>
       </c>
       <c r="K11" s="2">
-        <v>61380000.000000007</v>
+        <v>22330000</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -855,34 +851,34 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>18590000</v>
+        <v>9800000</v>
       </c>
       <c r="C12" s="2">
-        <v>18810000</v>
+        <v>10920000</v>
       </c>
       <c r="D12" s="2">
-        <v>27500000.000000004</v>
+        <v>11130000</v>
       </c>
       <c r="E12" s="2">
-        <v>73040000</v>
+        <v>10640000</v>
       </c>
       <c r="F12" s="2">
-        <v>92950000.000000015</v>
+        <v>10640000</v>
       </c>
       <c r="G12" s="2">
-        <v>64900000.000000007</v>
+        <v>10430000</v>
       </c>
       <c r="H12" s="2">
-        <v>42350000</v>
+        <v>9660000</v>
       </c>
       <c r="I12" s="2">
-        <v>42460000</v>
+        <v>9590000</v>
       </c>
       <c r="J12" s="2">
-        <v>33770000</v>
+        <v>9730000</v>
       </c>
       <c r="K12" s="2">
-        <v>35090000</v>
+        <v>9800000</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -890,34 +886,34 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>15400000.000000002</v>
+        <v>63419999.999999993</v>
       </c>
       <c r="C13" s="2">
-        <v>17160000</v>
+        <v>75600000</v>
       </c>
       <c r="D13" s="2">
-        <v>17490000</v>
+        <v>84700000</v>
       </c>
       <c r="E13" s="2">
-        <v>16720000.000000002</v>
+        <v>83300000</v>
       </c>
       <c r="F13" s="2">
-        <v>16720000.000000002</v>
+        <v>89600000</v>
       </c>
       <c r="G13" s="2">
-        <v>16390000.000000002</v>
+        <v>88900000</v>
       </c>
       <c r="H13" s="2">
-        <v>15180000.000000002</v>
+        <v>90300000</v>
       </c>
       <c r="I13" s="2">
-        <v>15070000.000000002</v>
+        <v>88200000</v>
       </c>
       <c r="J13" s="2">
-        <v>15290000.000000002</v>
+        <v>88900000</v>
       </c>
       <c r="K13" s="2">
-        <v>15400000.000000002</v>
+        <v>88900000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -925,34 +921,34 @@
         <v>6</v>
       </c>
       <c r="B14" s="2">
-        <v>15290000.000000002</v>
+        <v>43540000</v>
       </c>
       <c r="C14" s="2">
-        <v>16720000.000000002</v>
+        <v>52360000</v>
       </c>
       <c r="D14" s="2">
-        <v>17380000</v>
+        <v>51170000</v>
       </c>
       <c r="E14" s="2">
-        <v>18700000</v>
+        <v>46830000</v>
       </c>
       <c r="F14" s="2">
-        <v>19470000</v>
+        <v>48860000</v>
       </c>
       <c r="G14" s="2">
-        <v>17710000</v>
+        <v>41090000</v>
       </c>
       <c r="H14" s="2">
-        <v>1749000.0000000002</v>
+        <v>30799999.999999996</v>
       </c>
       <c r="I14" s="2">
-        <v>1749000.0000000002</v>
+        <v>29260000</v>
       </c>
       <c r="J14" s="2">
-        <v>1397000</v>
+        <v>29679999.999999996</v>
       </c>
       <c r="K14" s="2">
-        <v>1452000.0000000002</v>
+        <v>29959999.999999996</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -960,34 +956,34 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>12760000.000000002</v>
+        <v>63349999.999999993</v>
       </c>
       <c r="C15" s="2">
-        <v>17490000</v>
+        <v>81900000</v>
       </c>
       <c r="D15" s="2">
-        <v>20460000</v>
+        <v>91700000</v>
       </c>
       <c r="E15" s="2">
-        <v>20350000</v>
+        <v>91000000</v>
       </c>
       <c r="F15" s="2">
-        <v>20350000</v>
+        <v>91000000</v>
       </c>
       <c r="G15" s="2">
-        <v>20020000</v>
+        <v>89600000</v>
       </c>
       <c r="H15" s="2">
-        <v>20460000</v>
+        <v>69930000</v>
       </c>
       <c r="I15" s="2">
-        <v>20130000</v>
+        <v>68810000</v>
       </c>
       <c r="J15" s="2">
-        <v>20460000</v>
+        <v>70000000</v>
       </c>
       <c r="K15" s="2">
-        <v>20790000</v>
+        <v>71400000</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -995,34 +991,34 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>8173000.0000000009</v>
+        <v>557900000</v>
       </c>
       <c r="C16" s="2">
-        <v>11220000</v>
+        <v>572600000</v>
       </c>
       <c r="D16" s="2">
-        <v>13090000.000000002</v>
+        <v>597800000</v>
       </c>
       <c r="E16" s="2">
-        <v>13090000.000000002</v>
+        <v>553700000</v>
       </c>
       <c r="F16" s="2">
-        <v>12980000.000000002</v>
+        <v>571900000</v>
       </c>
       <c r="G16" s="2">
-        <v>12870000.000000002</v>
+        <v>572600000</v>
       </c>
       <c r="H16" s="2">
-        <v>13090000.000000002</v>
+        <v>377300000</v>
       </c>
       <c r="I16" s="2">
-        <v>12870000.000000002</v>
+        <v>434000000</v>
       </c>
       <c r="J16" s="2">
-        <v>13090000.000000002</v>
+        <v>385700000</v>
       </c>
       <c r="K16" s="2">
-        <v>13310000.000000002</v>
+        <v>406700000</v>
       </c>
     </row>
   </sheetData>
@@ -1031,18 +1027,6 @@
       <sortCondition descending="1" ref="B1:B16"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="A2:B16">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
